--- a/navneleg-demo/planets/planeter_demo.xlsx
+++ b/navneleg-demo/planets/planeter_demo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planeter" sheetId="1" r:id="Rdb7c20e717814988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planeter" sheetId="1" r:id="Rd8efdd320e9d4013"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1D4ED8"/>
+        <x:fgColor rgb="FF2563EB"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -78,23 +78,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PlaneterTable" displayName="PlaneterTable" ref="A1:I13" headerRowCount="1">
-  <x:tableColumns count="9">
-    <x:tableColumn id="1" name="KortID"/>
-    <x:tableColumn id="2" name="Billedfil"/>
-    <x:tableColumn id="3" name="Billedsti"/>
-    <x:tableColumn id="4" name="English"/>
-    <x:tableColumn id="5" name="Dansk"/>
-    <x:tableColumn id="6" name="OrderFromSun"/>
-    <x:tableColumn id="7" name="Type"/>
-    <x:tableColumn id="8" name="Hint"/>
-    <x:tableColumn id="9" name="Bagside"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -246,18 +229,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>KortID</x:v>
       </x:c>
@@ -268,21 +252,24 @@
         <x:v>Billedsti</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
+        <x:v>Forside</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
         <x:v>English</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>Dansk</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>OrderFromSun</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="I1" s="6" t="str">
         <x:v>Hint</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="J1" s="6" t="str">
         <x:v>Bagside</x:v>
       </x:c>
     </x:row>
@@ -297,21 +284,24 @@
         <x:v>navneleg-demo/planets/photos/01_mercury.png</x:v>
       </x:c>
       <x:c r="D2" s="12" t="str">
+        <x:v>Merkur</x:v>
+      </x:c>
+      <x:c r="E2" s="12" t="str">
         <x:v>Mercury</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="F2" s="12" t="str">
         <x:v>Merkur</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="G2" s="12" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
       <x:c r="H2" s="12" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I2" s="12" t="str">
         <x:v>Small and speedy.</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="J2" s="12" t="str">
         <x:v>Mercury · Planet</x:v>
       </x:c>
     </x:row>
@@ -332,15 +322,18 @@
         <x:v>Venus</x:v>
       </x:c>
       <x:c r="F3" s="12" t="str">
+        <x:v>Venus</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
       <x:c r="H3" s="12" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="str">
         <x:v>Greenhouse champion.</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
+      <x:c r="J3" s="12" t="str">
         <x:v>Venus · Planet</x:v>
       </x:c>
     </x:row>
@@ -355,21 +348,24 @@
         <x:v>navneleg-demo/planets/photos/03_earth.png</x:v>
       </x:c>
       <x:c r="D4" s="12" t="str">
+        <x:v>Jorden</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="str">
         <x:v>Earth</x:v>
       </x:c>
-      <x:c r="E4" s="12" t="str">
+      <x:c r="F4" s="12" t="str">
         <x:v>Jorden</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="str">
+      <x:c r="G4" s="12" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G4" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
       <x:c r="H4" s="12" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="str">
         <x:v>Currently occupied.</x:v>
       </x:c>
-      <x:c r="I4" s="12" t="str">
+      <x:c r="J4" s="12" t="str">
         <x:v>Earth · Planet</x:v>
       </x:c>
     </x:row>
@@ -390,15 +386,18 @@
         <x:v>Mars</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
+        <x:v>Mars</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
       <x:c r="H5" s="12" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
         <x:v>Red dust enthusiast.</x:v>
       </x:c>
-      <x:c r="I5" s="12" t="str">
+      <x:c r="J5" s="12" t="str">
         <x:v>Mars · Planet</x:v>
       </x:c>
     </x:row>
@@ -419,15 +418,18 @@
         <x:v>Jupiter</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
+        <x:v>Jupiter</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
       <x:c r="H6" s="12" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I6" s="12" t="str">
         <x:v>Big storm, bigger personality.</x:v>
       </x:c>
-      <x:c r="I6" s="12" t="str">
+      <x:c r="J6" s="12" t="str">
         <x:v>Jupiter · Planet</x:v>
       </x:c>
     </x:row>
@@ -448,15 +450,18 @@
         <x:v>Saturn</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
+        <x:v>Saturn</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
       <x:c r="H7" s="12" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="str">
         <x:v>Clearly accessorized.</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="str">
+      <x:c r="J7" s="12" t="str">
         <x:v>Saturn · Planet</x:v>
       </x:c>
     </x:row>
@@ -477,15 +482,18 @@
         <x:v>Uranus</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str">
+        <x:v>Uranus</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
       <x:c r="H8" s="12" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
         <x:v>Rolls sideways through life.</x:v>
       </x:c>
-      <x:c r="I8" s="12" t="str">
+      <x:c r="J8" s="12" t="str">
         <x:v>Uranus · Planet</x:v>
       </x:c>
     </x:row>
@@ -500,21 +508,24 @@
         <x:v>navneleg-demo/planets/photos/08_neptune.png</x:v>
       </x:c>
       <x:c r="D9" s="12" t="str">
+        <x:v>Neptun</x:v>
+      </x:c>
+      <x:c r="E9" s="12" t="str">
         <x:v>Neptune</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="str">
+      <x:c r="F9" s="12" t="str">
         <x:v>Neptun</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="str">
+      <x:c r="G9" s="12" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
       <x:c r="H9" s="12" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="str">
         <x:v>Windy blue mystery.</x:v>
       </x:c>
-      <x:c r="I9" s="12" t="str">
+      <x:c r="J9" s="12" t="str">
         <x:v>Neptune · Planet</x:v>
       </x:c>
     </x:row>
@@ -529,19 +540,22 @@
         <x:v>navneleg-demo/planets/photos/09_the_moon.png</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
+        <x:v>Månen</x:v>
+      </x:c>
+      <x:c r="E10" s="12" t="str">
         <x:v>The Moon</x:v>
       </x:c>
-      <x:c r="E10" s="12" t="str">
+      <x:c r="F10" s="12" t="str">
         <x:v>Månen</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="str"/>
-      <x:c r="G10" s="12" t="str">
+      <x:c r="G10" s="12" t="str"/>
+      <x:c r="H10" s="12" t="str">
         <x:v>Moon</x:v>
       </x:c>
-      <x:c r="H10" s="12" t="str">
+      <x:c r="I10" s="12" t="str">
         <x:v>Night shift reflector.</x:v>
       </x:c>
-      <x:c r="I10" s="12" t="str">
+      <x:c r="J10" s="12" t="str">
         <x:v>The Moon · Moon</x:v>
       </x:c>
     </x:row>
@@ -556,19 +570,22 @@
         <x:v>navneleg-demo/planets/photos/10_the_sun.png</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
+        <x:v>Solen</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="str">
         <x:v>The Sun</x:v>
       </x:c>
-      <x:c r="E11" s="12" t="str">
+      <x:c r="F11" s="12" t="str">
         <x:v>Solen</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="str"/>
-      <x:c r="G11" s="12" t="str">
+      <x:c r="G11" s="12" t="str"/>
+      <x:c r="H11" s="12" t="str">
         <x:v>Star</x:v>
       </x:c>
-      <x:c r="H11" s="12" t="str">
+      <x:c r="I11" s="12" t="str">
         <x:v>Classroom lamp, solar edition.</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="str">
+      <x:c r="J11" s="12" t="str">
         <x:v>The Sun · Star</x:v>
       </x:c>
     </x:row>
@@ -589,15 +606,18 @@
         <x:v>Pluto</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str">
+        <x:v>Pluto</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="str">
+      <x:c r="H12" s="12" t="str">
         <x:v>Dwarf planet</x:v>
       </x:c>
-      <x:c r="H12" s="12" t="str">
+      <x:c r="I12" s="12" t="str">
         <x:v>Still invited to demo parties.</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="str">
+      <x:c r="J12" s="12" t="str">
         <x:v>Pluto · Dwarf planet</x:v>
       </x:c>
     </x:row>
@@ -617,21 +637,21 @@
       <x:c r="E13" s="12" t="str">
         <x:v>Ceres</x:v>
       </x:c>
-      <x:c r="F13" s="12" t="str"/>
-      <x:c r="G13" s="12" t="str">
+      <x:c r="F13" s="12" t="str">
+        <x:v>Ceres</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="str"/>
+      <x:c r="H13" s="12" t="str">
         <x:v>Dwarf planet</x:v>
       </x:c>
-      <x:c r="H13" s="12" t="str">
+      <x:c r="I13" s="12" t="str">
         <x:v>Small, round, and responsible.</x:v>
       </x:c>
-      <x:c r="I13" s="12" t="str">
+      <x:c r="J13" s="12" t="str">
         <x:v>Ceres · Dwarf planet</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35daed719aef4f3b"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/navneleg-demo/planets/planeter_demo.xlsx
+++ b/navneleg-demo/planets/planeter_demo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planeter" sheetId="1" r:id="Rd8efdd320e9d4013"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planeter" sheetId="1" r:id="Raffd52d5135a4821"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2563EB"/>
+        <x:fgColor rgb="FF1D4ED8"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -45,30 +45,24 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -78,6 +72,24 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PlaneterTable" displayName="PlaneterTable" ref="A1:J13" headerRowCount="1">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="KortID"/>
+    <x:tableColumn id="2" name="Billedfil"/>
+    <x:tableColumn id="3" name="Billedsti"/>
+    <x:tableColumn id="4" name="Forside"/>
+    <x:tableColumn id="5" name="English"/>
+    <x:tableColumn id="6" name="Dansk"/>
+    <x:tableColumn id="7" name="OrderFromSun"/>
+    <x:tableColumn id="8" name="Type"/>
+    <x:tableColumn id="9" name="Hint"/>
+    <x:tableColumn id="10" name="Bagside"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -229,429 +241,408 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>KortID</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Billedfil</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Billedsti</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Forside</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>English</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Dansk</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>OrderFromSun</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>Hint</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="5" t="str">
         <x:v>Bagside</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="10" t="str">
         <x:v>SP01</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="10" t="str">
         <x:v>01_mercury.png</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/01_mercury.png</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="10" t="str"/>
+      <x:c r="E2" s="10" t="str">
+        <x:v>Mercury</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="str">
         <x:v>Merkur</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="G2" s="10" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="10" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I2" s="10" t="str">
+        <x:v>Small and speedy.</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="str">
         <x:v>Mercury</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
-        <x:v>Merkur</x:v>
-      </x:c>
-      <x:c r="G2" s="12" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
-      <x:c r="I2" s="12" t="str">
-        <x:v>Small and speedy.</x:v>
-      </x:c>
-      <x:c r="J2" s="12" t="str">
-        <x:v>Mercury · Planet</x:v>
-      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="10" t="str">
         <x:v>SP02</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="10" t="str">
         <x:v>02_venus.png</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/02_venus.png</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="10" t="str"/>
+      <x:c r="E3" s="10" t="str">
         <x:v>Venus</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="str">
+      <x:c r="F3" s="10" t="str">
         <x:v>Venus</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="G3" s="10" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="str">
+        <x:v>Greenhouse champion.</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="str">
         <x:v>Venus</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H3" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="str">
-        <x:v>Greenhouse champion.</x:v>
-      </x:c>
-      <x:c r="J3" s="12" t="str">
-        <x:v>Venus · Planet</x:v>
-      </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="12" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>SP03</x:v>
       </x:c>
-      <x:c r="B4" s="12" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>03_earth.png</x:v>
       </x:c>
-      <x:c r="C4" s="12" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/03_earth.png</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str">
+      <x:c r="D4" s="10" t="str"/>
+      <x:c r="E4" s="10" t="str">
+        <x:v>Earth</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
         <x:v>Jorden</x:v>
       </x:c>
-      <x:c r="E4" s="12" t="str">
+      <x:c r="G4" s="10" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="str">
+        <x:v>Currently occupied.</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="str">
         <x:v>Earth</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="str">
-        <x:v>Jorden</x:v>
-      </x:c>
-      <x:c r="G4" s="12" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H4" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
-      <x:c r="I4" s="12" t="str">
-        <x:v>Currently occupied.</x:v>
-      </x:c>
-      <x:c r="J4" s="12" t="str">
-        <x:v>Earth · Planet</x:v>
-      </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="12" t="str">
+      <x:c r="A5" s="10" t="str">
         <x:v>SP04</x:v>
       </x:c>
-      <x:c r="B5" s="12" t="str">
+      <x:c r="B5" s="10" t="str">
         <x:v>04_mars.png</x:v>
       </x:c>
-      <x:c r="C5" s="12" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/04_mars.png</x:v>
       </x:c>
-      <x:c r="D5" s="12" t="str">
+      <x:c r="D5" s="10" t="str"/>
+      <x:c r="E5" s="10" t="str">
         <x:v>Mars</x:v>
       </x:c>
-      <x:c r="E5" s="12" t="str">
+      <x:c r="F5" s="10" t="str">
         <x:v>Mars</x:v>
       </x:c>
-      <x:c r="F5" s="12" t="str">
+      <x:c r="G5" s="10" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="str">
+        <x:v>Red dust enthusiast.</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="str">
         <x:v>Mars</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H5" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
-      <x:c r="I5" s="12" t="str">
-        <x:v>Red dust enthusiast.</x:v>
-      </x:c>
-      <x:c r="J5" s="12" t="str">
-        <x:v>Mars · Planet</x:v>
-      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="12" t="str">
+      <x:c r="A6" s="10" t="str">
         <x:v>SP05</x:v>
       </x:c>
-      <x:c r="B6" s="12" t="str">
+      <x:c r="B6" s="10" t="str">
         <x:v>05_jupiter.png</x:v>
       </x:c>
-      <x:c r="C6" s="12" t="str">
+      <x:c r="C6" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/05_jupiter.png</x:v>
       </x:c>
-      <x:c r="D6" s="12" t="str">
+      <x:c r="D6" s="10" t="str"/>
+      <x:c r="E6" s="10" t="str">
         <x:v>Jupiter</x:v>
       </x:c>
-      <x:c r="E6" s="12" t="str">
+      <x:c r="F6" s="10" t="str">
         <x:v>Jupiter</x:v>
       </x:c>
-      <x:c r="F6" s="12" t="str">
+      <x:c r="G6" s="10" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H6" s="10" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I6" s="10" t="str">
+        <x:v>Big storm, bigger personality.</x:v>
+      </x:c>
+      <x:c r="J6" s="10" t="str">
         <x:v>Jupiter</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H6" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
-      <x:c r="I6" s="12" t="str">
-        <x:v>Big storm, bigger personality.</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="str">
-        <x:v>Jupiter · Planet</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="12" t="str">
+      <x:c r="A7" s="10" t="str">
         <x:v>SP06</x:v>
       </x:c>
-      <x:c r="B7" s="12" t="str">
+      <x:c r="B7" s="10" t="str">
         <x:v>06_saturn.png</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="str">
+      <x:c r="C7" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/06_saturn.png</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="str">
+      <x:c r="D7" s="10" t="str"/>
+      <x:c r="E7" s="10" t="str">
         <x:v>Saturn</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="str">
+      <x:c r="F7" s="10" t="str">
         <x:v>Saturn</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="str">
+      <x:c r="G7" s="10" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="str">
+        <x:v>Clearly accessorized.</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="str">
         <x:v>Saturn</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H7" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
-      <x:c r="I7" s="12" t="str">
-        <x:v>Clearly accessorized.</x:v>
-      </x:c>
-      <x:c r="J7" s="12" t="str">
-        <x:v>Saturn · Planet</x:v>
-      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="12" t="str">
+      <x:c r="A8" s="10" t="str">
         <x:v>SP07</x:v>
       </x:c>
-      <x:c r="B8" s="12" t="str">
+      <x:c r="B8" s="10" t="str">
         <x:v>07_uranus.png</x:v>
       </x:c>
-      <x:c r="C8" s="12" t="str">
+      <x:c r="C8" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/07_uranus.png</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="str">
+      <x:c r="D8" s="10" t="str"/>
+      <x:c r="E8" s="10" t="str">
         <x:v>Uranus</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="str">
+      <x:c r="F8" s="10" t="str">
         <x:v>Uranus</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="str">
+      <x:c r="G8" s="10" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H8" s="10" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I8" s="10" t="str">
+        <x:v>Rolls sideways through life.</x:v>
+      </x:c>
+      <x:c r="J8" s="10" t="str">
         <x:v>Uranus</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H8" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
-      <x:c r="I8" s="12" t="str">
-        <x:v>Rolls sideways through life.</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="str">
-        <x:v>Uranus · Planet</x:v>
-      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="12" t="str">
+      <x:c r="A9" s="10" t="str">
         <x:v>SP08</x:v>
       </x:c>
-      <x:c r="B9" s="12" t="str">
+      <x:c r="B9" s="10" t="str">
         <x:v>08_neptune.png</x:v>
       </x:c>
-      <x:c r="C9" s="12" t="str">
+      <x:c r="C9" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/08_neptune.png</x:v>
       </x:c>
-      <x:c r="D9" s="12" t="str">
+      <x:c r="D9" s="10" t="str"/>
+      <x:c r="E9" s="10" t="str">
+        <x:v>Neptune</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="str">
         <x:v>Neptun</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="str">
+      <x:c r="G9" s="10" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H9" s="10" t="str">
+        <x:v>Planet</x:v>
+      </x:c>
+      <x:c r="I9" s="10" t="str">
+        <x:v>Windy blue mystery.</x:v>
+      </x:c>
+      <x:c r="J9" s="10" t="str">
         <x:v>Neptune</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="str">
-        <x:v>Neptun</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H9" s="12" t="str">
-        <x:v>Planet</x:v>
-      </x:c>
-      <x:c r="I9" s="12" t="str">
-        <x:v>Windy blue mystery.</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="str">
-        <x:v>Neptune · Planet</x:v>
-      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="12" t="str">
+      <x:c r="A10" s="10" t="str">
         <x:v>SP09</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="str">
+      <x:c r="B10" s="10" t="str">
         <x:v>09_the_moon.png</x:v>
       </x:c>
-      <x:c r="C10" s="12" t="str">
+      <x:c r="C10" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/09_the_moon.png</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="str">
+      <x:c r="D10" s="10" t="str"/>
+      <x:c r="E10" s="10" t="str">
+        <x:v>The Moon</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="str">
         <x:v>Månen</x:v>
       </x:c>
-      <x:c r="E10" s="12" t="str">
+      <x:c r="G10" s="10" t="str"/>
+      <x:c r="H10" s="10" t="str">
+        <x:v>Moon</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str">
+        <x:v>Night shift reflector.</x:v>
+      </x:c>
+      <x:c r="J10" s="10" t="str">
         <x:v>The Moon</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="str">
-        <x:v>Månen</x:v>
-      </x:c>
-      <x:c r="G10" s="12" t="str"/>
-      <x:c r="H10" s="12" t="str">
-        <x:v>Moon</x:v>
-      </x:c>
-      <x:c r="I10" s="12" t="str">
-        <x:v>Night shift reflector.</x:v>
-      </x:c>
-      <x:c r="J10" s="12" t="str">
-        <x:v>The Moon · Moon</x:v>
-      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="12" t="str">
+      <x:c r="A11" s="10" t="str">
         <x:v>SP10</x:v>
       </x:c>
-      <x:c r="B11" s="12" t="str">
+      <x:c r="B11" s="10" t="str">
         <x:v>10_the_sun.png</x:v>
       </x:c>
-      <x:c r="C11" s="12" t="str">
+      <x:c r="C11" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/10_the_sun.png</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="str">
+      <x:c r="D11" s="10" t="str"/>
+      <x:c r="E11" s="10" t="str">
+        <x:v>The Sun</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="str">
         <x:v>Solen</x:v>
       </x:c>
-      <x:c r="E11" s="12" t="str">
+      <x:c r="G11" s="10" t="str"/>
+      <x:c r="H11" s="10" t="str">
+        <x:v>Star</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="str">
+        <x:v>Classroom lamp, solar edition.</x:v>
+      </x:c>
+      <x:c r="J11" s="10" t="str">
         <x:v>The Sun</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="str">
-        <x:v>Solen</x:v>
-      </x:c>
-      <x:c r="G11" s="12" t="str"/>
-      <x:c r="H11" s="12" t="str">
-        <x:v>Star</x:v>
-      </x:c>
-      <x:c r="I11" s="12" t="str">
-        <x:v>Classroom lamp, solar edition.</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="str">
-        <x:v>The Sun · Star</x:v>
-      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="12" t="str">
+      <x:c r="A12" s="10" t="str">
         <x:v>SP11</x:v>
       </x:c>
-      <x:c r="B12" s="12" t="str">
+      <x:c r="B12" s="10" t="str">
         <x:v>11_pluto.png</x:v>
       </x:c>
-      <x:c r="C12" s="12" t="str">
+      <x:c r="C12" s="10" t="str">
         <x:v>navneleg-demo/planets/photos/11_pluto.png</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="str">
+      <x:c r="D12" s="10" t="str"/>
+      <x:c r="E12" s="10" t="str">
         <x:v>Pluto</x:v>
       </x:c>
-      <x:c r="E12" s="12" t="str">
+      <x:c r="F12" s="10" t="str">
         <x:v>Pluto</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="str">
+      <x:c r="G12" s="10" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H12" s="10" t="str">
+        <x:v>Dwarf planet</x:v>
+      </x:c>
+      <x:c r="I12" s="10" t="str">
+        <x:v>Still invited to demo parties.</x:v>
+      </x:c>
+      <x:c r="J12" s="10" t="str">
         <x:v>Pluto</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H12" s="12" t="str">
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
+        <x:v>SP12</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>12_ceres.png</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
+        <x:v>navneleg-demo/planets/photos/12_ceres.png</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="str"/>
+      <x:c r="E13" s="10" t="str">
+        <x:v>Ceres</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="str">
+        <x:v>Ceres</x:v>
+      </x:c>
+      <x:c r="G13" s="10" t="str"/>
+      <x:c r="H13" s="10" t="str">
         <x:v>Dwarf planet</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="str">
-        <x:v>Still invited to demo parties.</x:v>
-      </x:c>
-      <x:c r="J12" s="12" t="str">
-        <x:v>Pluto · Dwarf planet</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="12" t="str">
-        <x:v>SP12</x:v>
-      </x:c>
-      <x:c r="B13" s="12" t="str">
-        <x:v>12_ceres.png</x:v>
-      </x:c>
-      <x:c r="C13" s="12" t="str">
-        <x:v>navneleg-demo/planets/photos/12_ceres.png</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="str">
+      <x:c r="I13" s="10" t="str">
+        <x:v>Small, round, and responsible.</x:v>
+      </x:c>
+      <x:c r="J13" s="10" t="str">
         <x:v>Ceres</x:v>
-      </x:c>
-      <x:c r="E13" s="12" t="str">
-        <x:v>Ceres</x:v>
-      </x:c>
-      <x:c r="F13" s="12" t="str">
-        <x:v>Ceres</x:v>
-      </x:c>
-      <x:c r="G13" s="12" t="str"/>
-      <x:c r="H13" s="12" t="str">
-        <x:v>Dwarf planet</x:v>
-      </x:c>
-      <x:c r="I13" s="12" t="str">
-        <x:v>Small, round, and responsible.</x:v>
-      </x:c>
-      <x:c r="J13" s="12" t="str">
-        <x:v>Ceres · Dwarf planet</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f33f59379a640ce"/>
+  </x:tableParts>
 </x:worksheet>
 </file>